--- a/Pedidos23.10 comerciales.xlsx
+++ b/Pedidos23.10 comerciales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agroquimicacodiagro365-my.sharepoint.com/personal/oscar_ocampo_codiagro_com/Documents/Escritorio/Presupuesto 2026/Calsif Comerciales/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{4C004BF6-44F9-42ED-B901-C5A5F007E52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{586516DE-DA1A-425A-AA80-A366A38111C3}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="8_{4C004BF6-44F9-42ED-B901-C5A5F007E52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04AE665F-A942-4C55-87F5-38F29983DC16}"/>
   <bookViews>
     <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{98158736-BF56-4FFC-90E7-0D5AFB7C782B}"/>
   </bookViews>
@@ -838,20 +838,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -866,9 +863,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -915,14 +909,14 @@
     <sortCondition ref="A1:A92"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{79FFDC31-DA67-4C1C-BF5A-16A44C08086A}" uniqueName="1" name="FechaPedido" queryTableFieldId="1" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{79FFDC31-DA67-4C1C-BF5A-16A44C08086A}" uniqueName="1" name="FechaPedido" queryTableFieldId="1" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{B7A5BD2F-A0AA-4D2A-AD36-68A160353B28}" uniqueName="2" name="Ejercicio" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{26952493-0B9E-4422-B66B-6E40E050CBF9}" uniqueName="3" name="Serie" queryTableFieldId="3" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{26952493-0B9E-4422-B66B-6E40E050CBF9}" uniqueName="3" name="Serie" queryTableFieldId="3" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{10B4CFE4-809C-42C6-B2D5-9983FC62B930}" uniqueName="4" name="Pedido" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{E2FFA7F6-5091-4D5A-8A15-7B6B0DD7A244}" uniqueName="5" name="CodigoCliente" queryTableFieldId="5" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{BED21177-8E3E-4721-88F0-0FE6F8D4E245}" uniqueName="6" name="Cliente" queryTableFieldId="6" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{32594C1A-7418-4B58-8F9A-36634B58AFFC}" uniqueName="7" name="CodigoArticulo" queryTableFieldId="7" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{1F7F79D5-CC59-4DF9-BB7D-158F1ABA8184}" uniqueName="8" name="Articulo" queryTableFieldId="8" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{E2FFA7F6-5091-4D5A-8A15-7B6B0DD7A244}" uniqueName="5" name="CodigoCliente" queryTableFieldId="5" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{BED21177-8E3E-4721-88F0-0FE6F8D4E245}" uniqueName="6" name="Cliente" queryTableFieldId="6" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{32594C1A-7418-4B58-8F9A-36634B58AFFC}" uniqueName="7" name="CodigoArticulo" queryTableFieldId="7" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{1F7F79D5-CC59-4DF9-BB7D-158F1ABA8184}" uniqueName="8" name="Articulo" queryTableFieldId="8" dataDxfId="1"/>
     <tableColumn id="9" xr3:uid="{63FB6AB6-C078-4B20-B394-D439DB3BC7E9}" uniqueName="9" name="Pedidas" queryTableFieldId="9"/>
     <tableColumn id="10" xr3:uid="{EBACB453-ECDA-4A66-B124-BA30C6F33D8E}" uniqueName="10" name="Servidas" queryTableFieldId="10"/>
     <tableColumn id="11" xr3:uid="{7499DAFD-C12E-4ADE-8A95-08E6656FD3CD}" uniqueName="11" name="Pendientes" queryTableFieldId="11"/>
@@ -1256,13 +1250,13 @@
   <dimension ref="A1:P156"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.54296875" customWidth="1"/>
     <col min="6" max="6" width="38.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6328125" customWidth="1"/>
     <col min="8" max="8" width="41.7265625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.26953125" bestFit="1" customWidth="1"/>
@@ -1275,7 +1269,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -6837,7 +6831,12 @@
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A113" s="1"/>
+      <c r="A113" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B113">
+        <v>2026</v>
+      </c>
       <c r="D113">
         <v>148</v>
       </c>
@@ -6880,7 +6879,12 @@
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A114" s="1"/>
+      <c r="A114" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B114">
+        <v>2026</v>
+      </c>
       <c r="D114">
         <v>148</v>
       </c>
@@ -6923,7 +6927,12 @@
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A115" s="1"/>
+      <c r="A115" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B115">
+        <v>2026</v>
+      </c>
       <c r="D115">
         <v>148</v>
       </c>
@@ -6966,7 +6975,12 @@
       </c>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A116" s="1"/>
+      <c r="A116" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B116">
+        <v>2026</v>
+      </c>
       <c r="D116">
         <v>148</v>
       </c>
@@ -7009,7 +7023,12 @@
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A117" s="1"/>
+      <c r="A117" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B117">
+        <v>2026</v>
+      </c>
       <c r="D117">
         <v>148</v>
       </c>
@@ -7052,7 +7071,12 @@
       </c>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A118" s="1"/>
+      <c r="A118" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B118">
+        <v>2026</v>
+      </c>
       <c r="D118">
         <v>148</v>
       </c>
@@ -7095,7 +7119,12 @@
       </c>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A119" s="1"/>
+      <c r="A119" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B119">
+        <v>2026</v>
+      </c>
       <c r="D119">
         <v>148</v>
       </c>
@@ -7138,7 +7167,12 @@
       </c>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A120" s="1"/>
+      <c r="A120" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B120">
+        <v>2026</v>
+      </c>
       <c r="D120">
         <v>148</v>
       </c>
@@ -7181,7 +7215,12 @@
       </c>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A121" s="1"/>
+      <c r="A121" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B121">
+        <v>2026</v>
+      </c>
       <c r="D121">
         <v>148</v>
       </c>
@@ -7224,7 +7263,12 @@
       </c>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A122" s="1"/>
+      <c r="A122" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B122">
+        <v>2026</v>
+      </c>
       <c r="D122">
         <v>148</v>
       </c>
@@ -7267,7 +7311,12 @@
       </c>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A123" s="1"/>
+      <c r="A123" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B123">
+        <v>2026</v>
+      </c>
       <c r="D123">
         <v>148</v>
       </c>
@@ -7310,7 +7359,12 @@
       </c>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A124" s="1"/>
+      <c r="A124" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B124">
+        <v>2026</v>
+      </c>
       <c r="D124">
         <v>148</v>
       </c>
@@ -7353,7 +7407,12 @@
       </c>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A125" s="1"/>
+      <c r="A125" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B125">
+        <v>2026</v>
+      </c>
       <c r="D125">
         <v>148</v>
       </c>
@@ -7396,7 +7455,12 @@
       </c>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A126" s="1"/>
+      <c r="A126" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B126">
+        <v>2026</v>
+      </c>
       <c r="D126">
         <v>148</v>
       </c>
@@ -7439,7 +7503,12 @@
       </c>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A127" s="1"/>
+      <c r="A127" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B127">
+        <v>2026</v>
+      </c>
       <c r="D127">
         <v>148</v>
       </c>
@@ -7482,7 +7551,12 @@
       </c>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A128" s="1"/>
+      <c r="A128" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B128">
+        <v>2026</v>
+      </c>
       <c r="D128">
         <v>148</v>
       </c>
@@ -7525,7 +7599,12 @@
       </c>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A129" s="1"/>
+      <c r="A129" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B129">
+        <v>2026</v>
+      </c>
       <c r="D129">
         <v>148</v>
       </c>
@@ -7568,7 +7647,12 @@
       </c>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A130" s="1"/>
+      <c r="A130" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B130">
+        <v>2026</v>
+      </c>
       <c r="D130">
         <v>148</v>
       </c>
@@ -7611,7 +7695,12 @@
       </c>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A131" s="1"/>
+      <c r="A131" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B131">
+        <v>2026</v>
+      </c>
       <c r="D131">
         <v>148</v>
       </c>
@@ -7654,7 +7743,12 @@
       </c>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A132" s="1"/>
+      <c r="A132" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B132">
+        <v>2026</v>
+      </c>
       <c r="D132">
         <v>148</v>
       </c>
@@ -7697,7 +7791,12 @@
       </c>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A133" s="1"/>
+      <c r="A133" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B133">
+        <v>2026</v>
+      </c>
       <c r="D133">
         <v>148</v>
       </c>
@@ -7740,7 +7839,12 @@
       </c>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A134" s="1"/>
+      <c r="A134" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B134">
+        <v>2026</v>
+      </c>
       <c r="D134">
         <v>891</v>
       </c>
@@ -7783,7 +7887,12 @@
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A135" s="1"/>
+      <c r="A135" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B135">
+        <v>2026</v>
+      </c>
       <c r="D135">
         <v>891</v>
       </c>
@@ -7826,7 +7935,12 @@
       </c>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A136" s="1"/>
+      <c r="A136" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B136">
+        <v>2026</v>
+      </c>
       <c r="D136">
         <v>891</v>
       </c>
@@ -7869,7 +7983,12 @@
       </c>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A137" s="1"/>
+      <c r="A137" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B137">
+        <v>2026</v>
+      </c>
       <c r="D137">
         <v>891</v>
       </c>
@@ -7912,7 +8031,12 @@
       </c>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A138" s="1"/>
+      <c r="A138" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B138">
+        <v>2026</v>
+      </c>
       <c r="D138">
         <v>891</v>
       </c>
@@ -7955,7 +8079,12 @@
       </c>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A139" s="1"/>
+      <c r="A139" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B139">
+        <v>2026</v>
+      </c>
       <c r="D139">
         <v>892</v>
       </c>
@@ -7999,27 +8128,31 @@
       </c>
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A140" s="1"/>
-      <c r="C140" s="2"/>
+      <c r="A140" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B140">
+        <v>2026</v>
+      </c>
       <c r="D140">
         <v>893</v>
       </c>
-      <c r="E140" s="3" t="s">
+      <c r="E140" t="s">
         <v>51</v>
       </c>
-      <c r="F140" s="4" t="s">
+      <c r="F140" t="s">
         <v>52</v>
       </c>
-      <c r="G140" s="2" t="s">
+      <c r="G140" t="s">
         <v>129</v>
       </c>
-      <c r="H140" s="5" t="s">
+      <c r="H140" t="s">
         <v>130</v>
       </c>
-      <c r="I140" s="6">
+      <c r="I140">
         <v>300</v>
       </c>
-      <c r="J140" s="6">
+      <c r="J140">
         <v>300</v>
       </c>
       <c r="K140">
@@ -8043,27 +8176,31 @@
       </c>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A141" s="1"/>
-      <c r="C141" s="2"/>
+      <c r="A141" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B141">
+        <v>2026</v>
+      </c>
       <c r="D141">
         <v>893</v>
       </c>
-      <c r="E141" s="4" t="s">
+      <c r="E141" t="s">
         <v>51</v>
       </c>
-      <c r="F141" s="4" t="s">
+      <c r="F141" t="s">
         <v>52</v>
       </c>
-      <c r="G141" s="2" t="s">
+      <c r="G141" t="s">
         <v>151</v>
       </c>
-      <c r="H141" s="5" t="s">
+      <c r="H141" t="s">
         <v>152</v>
       </c>
-      <c r="I141" s="6">
+      <c r="I141">
         <v>300</v>
       </c>
-      <c r="J141" s="6">
+      <c r="J141">
         <v>300</v>
       </c>
       <c r="K141">
@@ -8075,7 +8212,7 @@
       <c r="M141">
         <v>0</v>
       </c>
-      <c r="N141" s="6">
+      <c r="N141">
         <f>LineasPedidoCliente[[#This Row],[Precio]]*LineasPedidoCliente[[#This Row],[Pedidas]]</f>
         <v>677.99999999999989</v>
       </c>
@@ -8087,21 +8224,25 @@
       </c>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A142" s="1"/>
-      <c r="C142" s="2"/>
+      <c r="A142" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B142">
+        <v>2026</v>
+      </c>
       <c r="D142">
         <v>149</v>
       </c>
-      <c r="E142" s="7" t="s">
+      <c r="E142" t="s">
         <v>229</v>
       </c>
-      <c r="F142" s="7" t="s">
+      <c r="F142" t="s">
         <v>230</v>
       </c>
-      <c r="G142" s="2" t="s">
+      <c r="G142" t="s">
         <v>231</v>
       </c>
-      <c r="H142" s="2" t="s">
+      <c r="H142" t="s">
         <v>236</v>
       </c>
       <c r="I142">
@@ -8131,21 +8272,25 @@
       </c>
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A143" s="1"/>
-      <c r="C143" s="2"/>
-      <c r="D143" s="6">
+      <c r="A143" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B143">
+        <v>2026</v>
+      </c>
+      <c r="D143">
         <v>149</v>
       </c>
-      <c r="E143" s="7" t="s">
+      <c r="E143" t="s">
         <v>229</v>
       </c>
-      <c r="F143" s="7" t="s">
+      <c r="F143" t="s">
         <v>230</v>
       </c>
-      <c r="G143" s="2" t="s">
+      <c r="G143" t="s">
         <v>232</v>
       </c>
-      <c r="H143" s="2" t="s">
+      <c r="H143" t="s">
         <v>237</v>
       </c>
       <c r="I143">
@@ -8163,7 +8308,7 @@
       <c r="M143">
         <v>0</v>
       </c>
-      <c r="N143" s="7">
+      <c r="N143">
         <f>LineasPedidoCliente[[#This Row],[Pedidas]]*LineasPedidoCliente[[#This Row],[Precio]]</f>
         <v>10080</v>
       </c>
@@ -8175,21 +8320,25 @@
       </c>
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A144" s="1"/>
-      <c r="C144" s="2"/>
-      <c r="D144" s="6">
+      <c r="A144" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B144">
+        <v>2026</v>
+      </c>
+      <c r="D144">
         <v>149</v>
       </c>
-      <c r="E144" s="7" t="s">
+      <c r="E144" t="s">
         <v>229</v>
       </c>
-      <c r="F144" s="7" t="s">
+      <c r="F144" t="s">
         <v>230</v>
       </c>
-      <c r="G144" s="2" t="s">
+      <c r="G144" t="s">
         <v>233</v>
       </c>
-      <c r="H144" s="2" t="s">
+      <c r="H144" t="s">
         <v>238</v>
       </c>
       <c r="I144">
@@ -8207,7 +8356,7 @@
       <c r="M144">
         <v>0</v>
       </c>
-      <c r="N144" s="7">
+      <c r="N144">
         <f>LineasPedidoCliente[[#This Row],[Pedidas]]*LineasPedidoCliente[[#This Row],[Precio]]</f>
         <v>5566</v>
       </c>
@@ -8219,21 +8368,25 @@
       </c>
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A145" s="1"/>
-      <c r="C145" s="2"/>
-      <c r="D145" s="6">
+      <c r="A145" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B145">
+        <v>2026</v>
+      </c>
+      <c r="D145">
         <v>149</v>
       </c>
-      <c r="E145" s="7" t="s">
+      <c r="E145" t="s">
         <v>229</v>
       </c>
-      <c r="F145" s="7" t="s">
+      <c r="F145" t="s">
         <v>230</v>
       </c>
-      <c r="G145" s="2" t="s">
+      <c r="G145" t="s">
         <v>234</v>
       </c>
-      <c r="H145" s="2" t="s">
+      <c r="H145" t="s">
         <v>239</v>
       </c>
       <c r="I145">
@@ -8251,7 +8404,7 @@
       <c r="M145">
         <v>0</v>
       </c>
-      <c r="N145" s="7">
+      <c r="N145">
         <f>LineasPedidoCliente[[#This Row],[Pedidas]]*LineasPedidoCliente[[#This Row],[Precio]]</f>
         <v>4540</v>
       </c>
@@ -8263,21 +8416,25 @@
       </c>
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A146" s="1"/>
-      <c r="C146" s="2"/>
-      <c r="D146" s="6">
+      <c r="A146" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B146">
+        <v>2026</v>
+      </c>
+      <c r="D146">
         <v>149</v>
       </c>
-      <c r="E146" s="7" t="s">
+      <c r="E146" t="s">
         <v>229</v>
       </c>
-      <c r="F146" s="7" t="s">
+      <c r="F146" t="s">
         <v>230</v>
       </c>
-      <c r="G146" s="2" t="s">
+      <c r="G146" t="s">
         <v>235</v>
       </c>
-      <c r="H146" s="2" t="s">
+      <c r="H146" t="s">
         <v>240</v>
       </c>
       <c r="I146">
@@ -8295,7 +8452,7 @@
       <c r="M146">
         <v>0</v>
       </c>
-      <c r="N146" s="7">
+      <c r="N146">
         <f>LineasPedidoCliente[[#This Row],[Pedidas]]*LineasPedidoCliente[[#This Row],[Precio]]</f>
         <v>6100</v>
       </c>
@@ -8307,21 +8464,25 @@
       </c>
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A147" s="1"/>
-      <c r="C147" s="2"/>
-      <c r="D147" s="6">
+      <c r="A147" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B147">
+        <v>2026</v>
+      </c>
+      <c r="D147">
         <v>149</v>
       </c>
-      <c r="E147" s="7" t="s">
+      <c r="E147" t="s">
         <v>229</v>
       </c>
-      <c r="F147" s="7" t="s">
+      <c r="F147" t="s">
         <v>230</v>
       </c>
-      <c r="G147" s="2" t="s">
+      <c r="G147" t="s">
         <v>105</v>
       </c>
-      <c r="H147" s="2" t="s">
+      <c r="H147" t="s">
         <v>241</v>
       </c>
       <c r="I147">
@@ -8339,7 +8500,7 @@
       <c r="M147">
         <v>0</v>
       </c>
-      <c r="N147" s="7">
+      <c r="N147">
         <f>LineasPedidoCliente[[#This Row],[Pedidas]]*LineasPedidoCliente[[#This Row],[Precio]]</f>
         <v>18150</v>
       </c>
@@ -8351,21 +8512,25 @@
       </c>
     </row>
     <row r="148" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A148" s="1"/>
-      <c r="C148" s="2"/>
+      <c r="A148" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B148">
+        <v>2026</v>
+      </c>
       <c r="D148">
         <v>149</v>
       </c>
-      <c r="E148" s="7" t="s">
+      <c r="E148" t="s">
         <v>229</v>
       </c>
-      <c r="F148" s="7" t="s">
+      <c r="F148" t="s">
         <v>230</v>
       </c>
-      <c r="G148" s="2" t="s">
+      <c r="G148" t="s">
         <v>232</v>
       </c>
-      <c r="H148" s="2" t="s">
+      <c r="H148" t="s">
         <v>237</v>
       </c>
       <c r="I148">
@@ -8395,21 +8560,25 @@
       </c>
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A149" s="1"/>
-      <c r="C149" s="2"/>
+      <c r="A149" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B149">
+        <v>2026</v>
+      </c>
       <c r="D149">
         <v>149</v>
       </c>
-      <c r="E149" s="7" t="s">
+      <c r="E149" t="s">
         <v>229</v>
       </c>
-      <c r="F149" s="7" t="s">
+      <c r="F149" t="s">
         <v>230</v>
       </c>
-      <c r="G149" s="2" t="s">
+      <c r="G149" t="s">
         <v>231</v>
       </c>
-      <c r="H149" s="2" t="s">
+      <c r="H149" t="s">
         <v>236</v>
       </c>
       <c r="I149">
@@ -8427,7 +8596,7 @@
       <c r="M149">
         <v>0</v>
       </c>
-      <c r="N149" s="7">
+      <c r="N149">
         <f>LineasPedidoCliente[[#This Row],[Precio]]*LineasPedidoCliente[[#This Row],[Pedidas]]</f>
         <v>5840</v>
       </c>
@@ -8439,21 +8608,25 @@
       </c>
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A150" s="1"/>
-      <c r="C150" s="2"/>
+      <c r="A150" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B150">
+        <v>2026</v>
+      </c>
       <c r="D150">
         <v>149</v>
       </c>
-      <c r="E150" s="7" t="s">
+      <c r="E150" t="s">
         <v>229</v>
       </c>
-      <c r="F150" s="7" t="s">
+      <c r="F150" t="s">
         <v>230</v>
       </c>
-      <c r="G150" s="2" t="s">
+      <c r="G150" t="s">
         <v>242</v>
       </c>
-      <c r="H150" s="2" t="s">
+      <c r="H150" t="s">
         <v>246</v>
       </c>
       <c r="I150">
@@ -8471,7 +8644,7 @@
       <c r="M150">
         <v>0</v>
       </c>
-      <c r="N150" s="7">
+      <c r="N150">
         <f>LineasPedidoCliente[[#This Row],[Precio]]*LineasPedidoCliente[[#This Row],[Pedidas]]</f>
         <v>3370</v>
       </c>
@@ -8483,21 +8656,25 @@
       </c>
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A151" s="1"/>
-      <c r="C151" s="2"/>
+      <c r="A151" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B151">
+        <v>2026</v>
+      </c>
       <c r="D151">
         <v>149</v>
       </c>
-      <c r="E151" s="7" t="s">
+      <c r="E151" t="s">
         <v>229</v>
       </c>
-      <c r="F151" s="7" t="s">
+      <c r="F151" t="s">
         <v>230</v>
       </c>
-      <c r="G151" s="2" t="s">
+      <c r="G151" t="s">
         <v>243</v>
       </c>
-      <c r="H151" s="2" t="s">
+      <c r="H151" t="s">
         <v>247</v>
       </c>
       <c r="I151">
@@ -8515,7 +8692,7 @@
       <c r="M151">
         <v>0</v>
       </c>
-      <c r="N151" s="7">
+      <c r="N151">
         <f>LineasPedidoCliente[[#This Row],[Precio]]*LineasPedidoCliente[[#This Row],[Pedidas]]</f>
         <v>2920</v>
       </c>
@@ -8527,21 +8704,25 @@
       </c>
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A152" s="1"/>
-      <c r="C152" s="2"/>
+      <c r="A152" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B152">
+        <v>2026</v>
+      </c>
       <c r="D152">
         <v>149</v>
       </c>
-      <c r="E152" s="7" t="s">
+      <c r="E152" t="s">
         <v>229</v>
       </c>
-      <c r="F152" s="7" t="s">
+      <c r="F152" t="s">
         <v>230</v>
       </c>
-      <c r="G152" s="2" t="s">
+      <c r="G152" t="s">
         <v>244</v>
       </c>
-      <c r="H152" s="2" t="s">
+      <c r="H152" t="s">
         <v>248</v>
       </c>
       <c r="I152">
@@ -8559,7 +8740,7 @@
       <c r="M152">
         <v>0</v>
       </c>
-      <c r="N152" s="7">
+      <c r="N152">
         <f>LineasPedidoCliente[[#This Row],[Precio]]*LineasPedidoCliente[[#This Row],[Pedidas]]</f>
         <v>5760</v>
       </c>
@@ -8571,21 +8752,25 @@
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A153" s="1"/>
-      <c r="C153" s="2"/>
+      <c r="A153" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B153">
+        <v>2026</v>
+      </c>
       <c r="D153">
         <v>149</v>
       </c>
-      <c r="E153" s="7" t="s">
+      <c r="E153" t="s">
         <v>229</v>
       </c>
-      <c r="F153" s="7" t="s">
+      <c r="F153" t="s">
         <v>230</v>
       </c>
-      <c r="G153" s="2" t="s">
+      <c r="G153" t="s">
         <v>235</v>
       </c>
-      <c r="H153" s="2" t="s">
+      <c r="H153" t="s">
         <v>240</v>
       </c>
       <c r="I153">
@@ -8603,7 +8788,7 @@
       <c r="M153">
         <v>0</v>
       </c>
-      <c r="N153" s="7">
+      <c r="N153">
         <f>LineasPedidoCliente[[#This Row],[Precio]]*LineasPedidoCliente[[#This Row],[Pedidas]]</f>
         <v>6100</v>
       </c>
@@ -8615,21 +8800,25 @@
       </c>
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A154" s="1"/>
-      <c r="C154" s="2"/>
+      <c r="A154" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B154">
+        <v>2026</v>
+      </c>
       <c r="D154">
         <v>149</v>
       </c>
-      <c r="E154" s="7" t="s">
+      <c r="E154" t="s">
         <v>229</v>
       </c>
-      <c r="F154" s="7" t="s">
+      <c r="F154" t="s">
         <v>230</v>
       </c>
-      <c r="G154" s="2" t="s">
+      <c r="G154" t="s">
         <v>150</v>
       </c>
-      <c r="H154" s="2" t="s">
+      <c r="H154" t="s">
         <v>249</v>
       </c>
       <c r="I154">
@@ -8647,7 +8836,7 @@
       <c r="M154">
         <v>0</v>
       </c>
-      <c r="N154" s="7">
+      <c r="N154">
         <f>LineasPedidoCliente[[#This Row],[Precio]]*LineasPedidoCliente[[#This Row],[Pedidas]]</f>
         <v>2380.8000000000002</v>
       </c>
@@ -8659,21 +8848,25 @@
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A155" s="1"/>
-      <c r="C155" s="2"/>
+      <c r="A155" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B155">
+        <v>2026</v>
+      </c>
       <c r="D155">
         <v>149</v>
       </c>
-      <c r="E155" s="7" t="s">
+      <c r="E155" t="s">
         <v>229</v>
       </c>
-      <c r="F155" s="7" t="s">
+      <c r="F155" t="s">
         <v>230</v>
       </c>
-      <c r="G155" s="2" t="s">
+      <c r="G155" t="s">
         <v>245</v>
       </c>
-      <c r="H155" s="2" t="s">
+      <c r="H155" t="s">
         <v>250</v>
       </c>
       <c r="I155">
@@ -8691,7 +8884,7 @@
       <c r="M155">
         <v>0</v>
       </c>
-      <c r="N155" s="7">
+      <c r="N155">
         <f>LineasPedidoCliente[[#This Row],[Precio]]*LineasPedidoCliente[[#This Row],[Pedidas]]</f>
         <v>4690</v>
       </c>
@@ -8703,21 +8896,25 @@
       </c>
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A156" s="1"/>
-      <c r="C156" s="2"/>
+      <c r="A156" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B156">
+        <v>2026</v>
+      </c>
       <c r="D156">
         <v>149</v>
       </c>
-      <c r="E156" s="7" t="s">
+      <c r="E156" t="s">
         <v>229</v>
       </c>
-      <c r="F156" s="7" t="s">
+      <c r="F156" t="s">
         <v>230</v>
       </c>
-      <c r="G156" s="2" t="s">
+      <c r="G156" t="s">
         <v>105</v>
       </c>
-      <c r="H156" s="2" t="s">
+      <c r="H156" t="s">
         <v>241</v>
       </c>
       <c r="I156">
@@ -8735,7 +8932,7 @@
       <c r="M156">
         <v>0</v>
       </c>
-      <c r="N156" s="7">
+      <c r="N156">
         <f>LineasPedidoCliente[[#This Row],[Precio]]*LineasPedidoCliente[[#This Row],[Pedidas]]</f>
         <v>18150</v>
       </c>
